--- a/测试用例/哈尔滨冰城医疗美容医院/处理后表格/6月__冰城6月账单.xlsx
+++ b/测试用例/哈尔滨冰城医疗美容医院/处理后表格/6月__冰城6月账单.xlsx
@@ -1505,10 +1505,10 @@
         <v>2</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -2405,10 +2405,10 @@
         <v>1</v>
       </c>
       <c r="J45" s="21" t="n">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
       <c r="K45" s="21" t="n">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="46">
